--- a/03_BOM/BOM_PSH24-000.00.xlsx
+++ b/03_BOM/BOM_PSH24-000.00.xlsx
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.19</v>
+        <v>0.1928</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>0.39</v>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>741.38</v>
+        <v>741.3792</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>741.38</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>0.0036</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>2.37</v>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0063</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0.36</v>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0086</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0.03</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0113</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>1.22</v>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.02</v>
+        <v>0.0172</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0.82</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.03</v>
+        <v>0.0323</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0.52</v>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.09</v>
+        <v>0.0921</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0.37</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0.04</v>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.23</v>
+        <v>0.2262</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0.45</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>0.0029</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0.01</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.48</v>
+        <v>0.4845</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>3.88</v>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.02</v>
+        <v>0.0241</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0.29</v>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.03</v>
+        <v>0.0333</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>14.33</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.04</v>
+        <v>0.0438</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>0.44</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.06</v>
+        <v>0.0571</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>1.14</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>0.26</v>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.08</v>
+        <v>0.0755</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>0.15</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0069</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>0.01</v>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0119</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>0.29</v>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0117</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>2.59</v>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.02</v>
+        <v>0.0175</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>0.42</v>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.03</v>
+        <v>0.0257</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>0.05</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.03</v>
+        <v>0.0344</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>0.28</v>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0665</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>3.19</v>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.11</v>
+        <v>0.113</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0.9</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4</v>
+        <v>0.4048</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>1.62</v>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>0</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.01</v>
+        <v>0.0136</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>0.11</v>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0081</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>0.01</v>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>0</v>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.08</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="G40" s="4" t="n">
         <v>0.08</v>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.01 — Профиль резиновый 1200×346,4, L=6276,8</t>
+          <t>PSH24-000.01 — Полотно гибкое (резина), s=5</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>89.18000000000001</v>
+        <v>89.1788</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>89.18000000000001</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2152,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.02 — Деталь 250,5×244×130,5</t>
+          <t>PSH24-000.02 — Панель гнутая, s=4,7</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2.17</v>
+        <v>2.168</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>2.17</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.02-01-Variant2 — Деталь 250,5×230,2×139</t>
+          <t>PSH24-000.02-01-Variant2 — Панель гнутая, s=4,7</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2.17</v>
+        <v>2.168</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>2.17</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.03 — Профиль сплошной 40×3, L=5600</t>
+          <t>PSH24-000.03 — Полоса 40×3, L=5600</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5.22</v>
+        <v>5.2237</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>10.45</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.04 — Профиль резиновый 171×32,8, L=5700</t>
+          <t>PSH24-000.04 — Полотно гибкое (резина), s=4,9</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5.78</v>
+        <v>5.7848</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>11.57</v>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.05 — Стержень ⌀63, L=1026</t>
+          <t>PSH24-000.05 — Деталь 1026×63×63</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
@@ -2329,11 +2329,11 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Комплектующее покупное (см. спецификацию)</t>
+          <t>Ст3сп5, ГОСТ 380-2005 (принято по умолчанию)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>24.53</v>
+        <v>24.5252</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>662.1799999999999</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>стержневая</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.06 — Труба ⌀108×13,1, L=1338</t>
+          <t>PSH24-000.06 — Деталь 1338×108×108</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
@@ -2370,11 +2370,11 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Комплектующее покупное (см. спецификацию)</t>
+          <t>Ст3сп5, ГОСТ 380-2005 (принято по умолчанию)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>41.06</v>
+        <v>41.063</v>
       </c>
       <c r="G47" s="4" t="n">
         <v>205.32</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2398,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.07 — Профиль сплошной 105×15, L=1260</t>
+          <t>PSH24-000.07 — Деталь 1260×105×15</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2.14</v>
+        <v>2.1361</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>2.14</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.08 — Профиль сплошной 40×3, L=1260</t>
+          <t>PSH24-000.08 — Полоса 40×3, L=1260</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.17</v>
+        <v>1.1668</v>
       </c>
       <c r="G49" s="4" t="n">
         <v>2.33</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.09 — Профиль сплошной 60×8, L=850</t>
+          <t>PSH24-000.09 — Полоса 60×8, L=850</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.38</v>
+        <v>0.384</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>0.77</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.10 — Профиль сплошной 40×3, L=850</t>
+          <t>PSH24-000.10 — Полоса 40×3, L=850</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.79</v>
+        <v>0.7873</v>
       </c>
       <c r="G51" s="4" t="n">
         <v>1.57</v>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>PSH24-000.11 — Профиль сплошной 105×8, L=1330</t>
+          <t>PSH24-000.11 — Полоса резиновая 105×8, L=1330</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1.28</v>
+        <v>1.2778</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>1.28</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>41.09</v>
+        <v>41.0947</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>41.09</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>0.22</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-001.01 — Труба профильная 168,7×62×2, L=5720</t>
+          <t xml:space="preserve">    PSH24-001.01 — Панель гнутая, s=4,8</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>40.88</v>
+        <v>40.8762</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>40.88</v>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>41.06</v>
+        <v>41.0567</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>41.06</v>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>0.18</v>
@@ -2808,12 +2808,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-001.01-01 — Труба профильная 168,7×62×2, L=5720</t>
+          <t xml:space="preserve">    PSH24-001.01-01 — Панель гнутая, s=4,8</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>40.88</v>
+        <v>40.8762</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>40.88</v>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>674.7</v>
+        <v>674.6969</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>674.7</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>7.29</v>
+        <v>7.2922</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>36.46</v>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.698700000000001</v>
       </c>
       <c r="G61" s="4" t="n">
         <v>34.79</v>
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.06</v>
+        <v>0.0582</v>
       </c>
       <c r="G62" s="4" t="n">
         <v>0.12</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-010.04 — Профиль сплошной 175×3, L=750</t>
+          <t xml:space="preserve">    PSH24-010.04 — Полоса 175×3, L=750</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3.04</v>
+        <v>3.039</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>6.08</v>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="F64" s="6" t="n">
-        <v>208.61</v>
+        <v>208.6075</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>208.61</v>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0052</v>
       </c>
       <c r="G65" s="4" t="n">
         <v>0.06</v>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        PSH24-011.01 — Труба профильная 451×105×3,3, L=3500</t>
+          <t xml:space="preserve">        PSH24-011.01 — Деталь 3500×451×105</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>100.67</v>
+        <v>100.6668</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>100.67</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.8904</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>9.890000000000001</v>
@@ -3259,12 +3259,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        PSH24-011.04 — Профиль сплошной 79×6, L=437</t>
+          <t xml:space="preserve">        PSH24-011.04 — Полоса 79×6, L=437</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1.62</v>
+        <v>1.624</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>9.74</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.98</v>
+        <v>0.9797</v>
       </c>
       <c r="G70" s="4" t="n">
         <v>1.96</v>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>17.08</v>
+        <v>17.0781</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>17.08</v>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        PSH24-011.07 — Труба профильная 451×105×3,5, L=2105</t>
+          <t xml:space="preserve">        PSH24-011.07 — Деталь 2105×451×105</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>63.4</v>
+        <v>63.3959</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>63.4</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>208.61</v>
+        <v>208.6086</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>208.61</v>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0052</v>
       </c>
       <c r="G74" s="4" t="n">
         <v>0.06</v>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        PSH24-011.01-01 — Труба профильная 451×105×3,3, L=3500</t>
+          <t xml:space="preserve">        PSH24-011.01-01 — Деталь 3500×451×105</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D75" s="4" t="n">
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>100.67</v>
+        <v>100.6668</v>
       </c>
       <c r="G75" s="4" t="n">
         <v>100.67</v>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.8904</v>
       </c>
       <c r="G77" s="4" t="n">
         <v>9.890000000000001</v>
@@ -3628,12 +3628,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        PSH24-011.04 — Профиль сплошной 79×6, L=437</t>
+          <t xml:space="preserve">        PSH24-011.04 — Полоса 79×6, L=437</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1.62</v>
+        <v>1.624</v>
       </c>
       <c r="G78" s="4" t="n">
         <v>9.74</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.98</v>
+        <v>0.9797</v>
       </c>
       <c r="G79" s="4" t="n">
         <v>1.96</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>17.08</v>
+        <v>17.0781</v>
       </c>
       <c r="G80" s="4" t="n">
         <v>17.08</v>
@@ -3751,12 +3751,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        PSH24-011.07-01 — Труба профильная 451×105×3,5, L=2105</t>
+          <t xml:space="preserve">        PSH24-011.07-01 — Деталь 2105×451×105</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>63.4</v>
+        <v>63.397</v>
       </c>
       <c r="G81" s="4" t="n">
         <v>63.4</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="F82" s="6" t="n">
-        <v>90.02</v>
+        <v>90.0154</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>90.02</v>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>53.39</v>
+        <v>53.3871</v>
       </c>
       <c r="G83" s="4" t="n">
         <v>53.39</v>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="G84" s="4" t="n">
         <v>5.95</v>
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>30.68</v>
+        <v>30.6758</v>
       </c>
       <c r="G85" s="4" t="n">
         <v>30.68</v>
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="F86" s="6" t="n">
-        <v>90.02</v>
+        <v>90.0154</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>90.02</v>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>53.39</v>
+        <v>53.3871</v>
       </c>
       <c r="G87" s="4" t="n">
         <v>53.39</v>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="G88" s="4" t="n">
         <v>5.95</v>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>30.68</v>
+        <v>30.6758</v>
       </c>
       <c r="G89" s="4" t="n">
         <v>30.68</v>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="F90" s="6" t="n">
-        <v>16.59</v>
+        <v>16.5893</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>16.59</v>
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>3.06</v>
+        <v>3.0626</v>
       </c>
       <c r="G91" s="4" t="n">
         <v>3.06</v>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>12.6</v>
+        <v>12.6023</v>
       </c>
       <c r="G92" s="4" t="n">
         <v>12.6</v>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>0.92</v>
+        <v>0.9244</v>
       </c>
       <c r="G93" s="4" t="n">
         <v>0.92</v>
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="F94" s="6" t="n">
-        <v>383.59</v>
+        <v>383.5906</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>383.59</v>
@@ -4325,12 +4325,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.01 — Деталь 1561,4×1250×138,1</t>
+          <t xml:space="preserve">    PSH24-021.01 — Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>83.78</v>
+        <v>83.7816</v>
       </c>
       <c r="G95" s="4" t="n">
         <v>251.34</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.02 — Труба профильная 112,9×5×1,5, L=1546,5</t>
+          <t xml:space="preserve">    PSH24-021.02 — Полоса 112,9×5, L=1546,5</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>4.3</v>
+        <v>4.3004</v>
       </c>
       <c r="G96" s="4" t="n">
         <v>8.6</v>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>26.31</v>
+        <v>26.3094</v>
       </c>
       <c r="G97" s="4" t="n">
         <v>78.93000000000001</v>
@@ -4448,12 +4448,12 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.04 — Труба профильная 112,9×5×1,4, L=1548</t>
+          <t xml:space="preserve">    PSH24-021.04 — Полоса 112,9×5, L=1548</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>3.81</v>
+        <v>3.8109</v>
       </c>
       <c r="G98" s="4" t="n">
         <v>19.05</v>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>0.89</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="G99" s="4" t="n">
         <v>8.91</v>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.06 — Труба профильная 250×138,1×1,8, L=1561,4</t>
+          <t xml:space="preserve">    PSH24-021.06 — Панель гнутая, s=4,9</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>16.76</v>
+        <v>16.7563</v>
       </c>
       <c r="G100" s="4" t="n">
         <v>16.76</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="F101" s="6" t="n">
-        <v>383.59</v>
+        <v>383.5906</v>
       </c>
       <c r="G101" s="6" t="n">
         <v>383.59</v>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.01 — Деталь 1561,4×1250×138,1</t>
+          <t xml:space="preserve">    PSH24-021.01 — Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>83.78</v>
+        <v>83.7816</v>
       </c>
       <c r="G102" s="4" t="n">
         <v>251.34</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.02 — Труба профильная 112,9×5×1,5, L=1546,5</t>
+          <t xml:space="preserve">    PSH24-021.02 — Полоса 112,9×5, L=1546,5</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>4.3</v>
+        <v>4.3004</v>
       </c>
       <c r="G103" s="4" t="n">
         <v>8.6</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>26.31</v>
+        <v>26.3094</v>
       </c>
       <c r="G104" s="4" t="n">
         <v>78.93000000000001</v>
@@ -4735,12 +4735,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.04 — Труба профильная 112,9×5×1,4, L=1548</t>
+          <t xml:space="preserve">    PSH24-021.04 — Полоса 112,9×5, L=1548</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>3.81</v>
+        <v>3.8109</v>
       </c>
       <c r="G105" s="4" t="n">
         <v>19.05</v>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>0.89</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="G106" s="4" t="n">
         <v>8.91</v>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.06 — Труба профильная 250×138,1×1,8, L=1561,4</t>
+          <t xml:space="preserve">    PSH24-021.06 — Панель гнутая, s=4,9</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D107" s="4" t="n">
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>16.76</v>
+        <v>16.7563</v>
       </c>
       <c r="G107" s="4" t="n">
         <v>16.76</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="F108" s="6" t="n">
-        <v>165.6</v>
+        <v>165.6015</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>165.6</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>114.41</v>
+        <v>114.4098</v>
       </c>
       <c r="G109" s="4" t="n">
         <v>114.41</v>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-022.02 — Профиль сплошной 80×6, L=1506</t>
+          <t xml:space="preserve">    PSH24-022.02 — Полоса 80×6, L=1506</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D110" s="4" t="n">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>5.64</v>
+        <v>5.6426</v>
       </c>
       <c r="G110" s="4" t="n">
         <v>5.64</v>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -4981,12 +4981,12 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-022.03 — Профиль сплошной 80×5, L=3004</t>
+          <t xml:space="preserve">    PSH24-022.03 — Полоса 80×5, L=3004</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D111" s="4" t="n">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.383699999999999</v>
       </c>
       <c r="G111" s="4" t="n">
         <v>9.380000000000001</v>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5022,12 +5022,12 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-022.04 — Профиль сплошной 80×6, L=1323</t>
+          <t xml:space="preserve">    PSH24-022.04 — Полоса 80×6, L=1323</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D112" s="4" t="n">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>4.99</v>
+        <v>4.9851</v>
       </c>
       <c r="G112" s="4" t="n">
         <v>9.970000000000001</v>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-022.05 — Профиль сплошной 80×6, L=800</t>
+          <t xml:space="preserve">    PSH24-022.05 — Полоса 80×6, L=800</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>3.01</v>
+        <v>3.0144</v>
       </c>
       <c r="G113" s="4" t="n">
         <v>6.03</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5104,12 +5104,12 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-022.06 — Профиль сплошной 80×6, L=743</t>
+          <t xml:space="preserve">    PSH24-022.06 — Полоса 80×6, L=743</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D114" s="4" t="n">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7996</v>
       </c>
       <c r="G114" s="4" t="n">
         <v>5.6</v>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-022.07 — Профиль сплошной 80×6, L=410</t>
+          <t xml:space="preserve">    PSH24-022.07 — Полоса 80×6, L=410</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1.54</v>
+        <v>1.5449</v>
       </c>
       <c r="G115" s="4" t="n">
         <v>3.09</v>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-022.08 — Профиль сплошной 80×6, L=1423</t>
+          <t xml:space="preserve">    PSH24-022.08 — Полоса 80×6, L=1423</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D116" s="4" t="n">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>5.36</v>
+        <v>5.3619</v>
       </c>
       <c r="G116" s="4" t="n">
         <v>10.72</v>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>0.38</v>
+        <v>0.3768</v>
       </c>
       <c r="G117" s="4" t="n">
         <v>0.75</v>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="F118" s="6" t="n">
-        <v>131.75</v>
+        <v>131.7518</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>131.75</v>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="G119" s="4" t="n">
         <v>0.11</v>
@@ -5350,12 +5350,12 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-022.03 — Профиль сплошной 80×5, L=3004</t>
+          <t xml:space="preserve">    PSH24-022.03 — Полоса 80×5, L=3004</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D120" s="4" t="n">
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.383699999999999</v>
       </c>
       <c r="G120" s="4" t="n">
         <v>9.380000000000001</v>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-022.08 — Профиль сплошной 80×6, L=1423</t>
+          <t xml:space="preserve">    PSH24-022.08 — Полоса 80×6, L=1423</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D121" s="4" t="n">
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>5.36</v>
+        <v>5.3619</v>
       </c>
       <c r="G121" s="4" t="n">
         <v>10.72</v>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>0.38</v>
+        <v>0.3768</v>
       </c>
       <c r="G122" s="4" t="n">
         <v>0.75</v>
@@ -5490,7 +5490,7 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>87.97</v>
+        <v>87.9691</v>
       </c>
       <c r="G123" s="4" t="n">
         <v>87.97</v>
@@ -5514,12 +5514,12 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-023.02 — Профиль сплошной 80×6, L=568</t>
+          <t xml:space="preserve">    PSH24-023.02 — Полоса 80×6, L=568</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D124" s="4" t="n">
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>2.14</v>
+        <v>2.1402</v>
       </c>
       <c r="G124" s="4" t="n">
         <v>4.28</v>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>0.89</v>
+        <v>0.8855</v>
       </c>
       <c r="G125" s="4" t="n">
         <v>1.77</v>
@@ -5596,12 +5596,12 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-023.04 — Профиль сплошной 80×6, L=1305</t>
+          <t xml:space="preserve">    PSH24-023.04 — Полоса 80×6, L=1305</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>4.9</v>
+        <v>4.8993</v>
       </c>
       <c r="G126" s="4" t="n">
         <v>9.800000000000001</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5637,12 +5637,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-023.05 — Профиль сплошной 80×6, L=1210</t>
+          <t xml:space="preserve">    PSH24-023.05 — Полоса 80×6, L=1210</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D127" s="4" t="n">
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>4.54</v>
+        <v>4.5379</v>
       </c>
       <c r="G127" s="4" t="n">
         <v>4.54</v>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5678,12 +5678,12 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-023.10 — Труба ⌀30×2, L=894</t>
+          <t xml:space="preserve">    PSH24-023.10 — Деталь 894×30×30</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D128" s="4" t="n">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1.21</v>
+        <v>1.2099</v>
       </c>
       <c r="G128" s="4" t="n">
         <v>2.42</v>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="F129" s="6" t="n">
-        <v>96.02</v>
+        <v>96.02079999999999</v>
       </c>
       <c r="G129" s="6" t="n">
         <v>96.02</v>
@@ -5760,12 +5760,12 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-024.01 — Труба профильная 600×85×2,8, L=3004</t>
+          <t xml:space="preserve">    PSH24-024.01 — Деталь 3004×600×85</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D130" s="4" t="n">
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="F130" s="4" t="n">
-        <v>88.63</v>
+        <v>88.62609999999999</v>
       </c>
       <c r="G130" s="4" t="n">
         <v>88.63</v>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -5801,12 +5801,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-024.02 — Профиль сплошной 80×5, L=590</t>
+          <t xml:space="preserve">    PSH24-024.02 — Полоса 80×5, L=590</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D131" s="4" t="n">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1.85</v>
+        <v>1.8487</v>
       </c>
       <c r="G131" s="4" t="n">
         <v>7.39</v>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="F132" s="6" t="n">
-        <v>96.02</v>
+        <v>96.02079999999999</v>
       </c>
       <c r="G132" s="6" t="n">
         <v>96.02</v>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-024.01_1 — Труба профильная 600×85×2,8, L=3004</t>
+          <t xml:space="preserve">    PSH24-024.01_1 — Деталь 3004×600×85</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D133" s="4" t="n">
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>88.63</v>
+        <v>88.62609999999999</v>
       </c>
       <c r="G133" s="4" t="n">
         <v>88.63</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-024.02 — Профиль сплошной 80×5, L=590</t>
+          <t xml:space="preserve">    PSH24-024.02 — Полоса 80×5, L=590</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D134" s="4" t="n">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1.85</v>
+        <v>1.8487</v>
       </c>
       <c r="G134" s="4" t="n">
         <v>7.39</v>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="F135" s="6" t="n">
-        <v>82.38</v>
+        <v>82.38209999999999</v>
       </c>
       <c r="G135" s="6" t="n">
         <v>329.53</v>
@@ -6006,12 +6006,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-024.02 — Профиль сплошной 80×5, L=590</t>
+          <t xml:space="preserve">    PSH24-024.02 — Полоса 80×5, L=590</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D136" s="4" t="n">
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1.85</v>
+        <v>1.8487</v>
       </c>
       <c r="G136" s="4" t="n">
         <v>5.55</v>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -6047,12 +6047,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-025.01 — Труба профильная 600×85×2,9, L=2500</t>
+          <t xml:space="preserve">    PSH24-025.01 — Деталь 2500×600×85</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D137" s="4" t="n">
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>76.84</v>
+        <v>76.836</v>
       </c>
       <c r="G137" s="4" t="n">
         <v>76.84</v>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="F138" s="6" t="n">
-        <v>99.89</v>
+        <v>99.8886</v>
       </c>
       <c r="G138" s="6" t="n">
         <v>99.89</v>
@@ -6129,12 +6129,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.02 — Труба профильная 112,9×5×1,5, L=1546,5</t>
+          <t xml:space="preserve">    PSH24-021.02 — Полоса 112,9×5, L=1546,5</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D139" s="4" t="n">
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>4.3</v>
+        <v>4.3004</v>
       </c>
       <c r="G139" s="4" t="n">
         <v>8.6</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.04 — Труба профильная 112,9×5×1,4, L=1548</t>
+          <t xml:space="preserve">    PSH24-021.04 — Полоса 112,9×5, L=1548</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D140" s="4" t="n">
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>3.81</v>
+        <v>3.8109</v>
       </c>
       <c r="G140" s="4" t="n">
         <v>3.81</v>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>0.89</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="G141" s="4" t="n">
         <v>0.89</v>
@@ -6252,12 +6252,12 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-026.01 — Деталь 1561,4×1000×138,1</t>
+          <t xml:space="preserve">    PSH24-026.01 — Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D142" s="4" t="n">
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="F142" s="4" t="n">
-        <v>67</v>
+        <v>67.0027</v>
       </c>
       <c r="G142" s="4" t="n">
         <v>67</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>6.53</v>
+        <v>6.5279</v>
       </c>
       <c r="G143" s="4" t="n">
         <v>19.58</v>
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="F144" s="6" t="n">
-        <v>99.89</v>
+        <v>99.8886</v>
       </c>
       <c r="G144" s="6" t="n">
         <v>99.89</v>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.02 — Труба профильная 112,9×5×1,5, L=1546,5</t>
+          <t xml:space="preserve">    PSH24-021.02 — Полоса 112,9×5, L=1546,5</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D145" s="4" t="n">
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>4.3</v>
+        <v>4.3004</v>
       </c>
       <c r="G145" s="4" t="n">
         <v>8.6</v>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -6416,12 +6416,12 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-021.04 — Труба профильная 112,9×5×1,4, L=1548</t>
+          <t xml:space="preserve">    PSH24-021.04 — Полоса 112,9×5, L=1548</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D146" s="4" t="n">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="F146" s="4" t="n">
-        <v>3.81</v>
+        <v>3.8109</v>
       </c>
       <c r="G146" s="4" t="n">
         <v>3.81</v>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>0.89</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0.89</v>
@@ -6498,12 +6498,12 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-026.01-01 — Деталь 1561,4×1000×138,1</t>
+          <t xml:space="preserve">    PSH24-026.01-01 — Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D148" s="4" t="n">
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>67</v>
+        <v>67.0027</v>
       </c>
       <c r="G148" s="4" t="n">
         <v>67</v>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>6.53</v>
+        <v>6.5279</v>
       </c>
       <c r="G149" s="4" t="n">
         <v>19.58</v>
@@ -6580,12 +6580,12 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>PSH24-030.01 — Труба профильная 80×45×4,9, L=2128</t>
+          <t>PSH24-030.01 — Деталь 2128×80×45</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D150" s="4" t="n">
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="F150" s="4" t="n">
-        <v>18.77</v>
+        <v>18.7717</v>
       </c>
       <c r="G150" s="4" t="n">
         <v>75.09</v>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -6621,12 +6621,12 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>PSH24-030.02 — Труба ⌀50×3,3, L=1410</t>
+          <t>PSH24-030.02 — Деталь 1410×50×50</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D151" s="4" t="n">
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>5.3</v>
+        <v>5.3036</v>
       </c>
       <c r="G151" s="4" t="n">
         <v>21.21</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>PSH24-030.04 — Труба ⌀50×3,3, L=1207</t>
+          <t>PSH24-030.04 — Деталь 1207×50×50</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D152" s="4" t="n">
@@ -6679,7 +6679,7 @@
         </is>
       </c>
       <c r="F152" s="4" t="n">
-        <v>4.53</v>
+        <v>4.5273</v>
       </c>
       <c r="G152" s="4" t="n">
         <v>18.11</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="F153" s="6" t="n">
-        <v>53.35</v>
+        <v>53.3514</v>
       </c>
       <c r="G153" s="6" t="n">
         <v>266.76</v>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="F154" s="4" t="n">
-        <v>0.03</v>
+        <v>0.0283</v>
       </c>
       <c r="G154" s="4" t="n">
         <v>0.68</v>
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>50.59</v>
+        <v>50.5934</v>
       </c>
       <c r="G155" s="4" t="n">
         <v>50.59</v>
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="F156" s="4" t="n">
-        <v>1.04</v>
+        <v>1.0395</v>
       </c>
       <c r="G156" s="4" t="n">
         <v>2.08</v>
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>15</v>
+        <v>14.9952</v>
       </c>
       <c r="G158" s="4" t="n">
         <v>29.99</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>14.99</v>
+        <v>14.986</v>
       </c>
       <c r="G159" s="4" t="n">
         <v>29.97</v>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>15.69</v>
+        <v>15.6882</v>
       </c>
       <c r="G160" s="4" t="n">
         <v>15.69</v>
@@ -7048,7 +7048,7 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>2.58</v>
+        <v>2.5838</v>
       </c>
       <c r="G161" s="4" t="n">
         <v>10.34</v>
@@ -7089,7 +7089,7 @@
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>1.33</v>
+        <v>1.3271</v>
       </c>
       <c r="G162" s="4" t="n">
         <v>2.65</v>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="F163" s="6" t="n">
-        <v>91.29000000000001</v>
+        <v>91.2942</v>
       </c>
       <c r="G163" s="6" t="n">
         <v>91.29000000000001</v>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>15</v>
+        <v>14.9952</v>
       </c>
       <c r="G164" s="4" t="n">
         <v>29.99</v>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>14.99</v>
+        <v>14.986</v>
       </c>
       <c r="G165" s="4" t="n">
         <v>29.97</v>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="F166" s="4" t="n">
-        <v>15.69</v>
+        <v>15.6882</v>
       </c>
       <c r="G166" s="4" t="n">
         <v>15.69</v>
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>2.58</v>
+        <v>2.5838</v>
       </c>
       <c r="G167" s="4" t="n">
         <v>10.34</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="F168" s="4" t="n">
-        <v>1.33</v>
+        <v>1.3271</v>
       </c>
       <c r="G168" s="4" t="n">
         <v>5.31</v>
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="F169" s="6" t="n">
-        <v>2.9</v>
+        <v>2.8957</v>
       </c>
       <c r="G169" s="6" t="n">
         <v>11.58</v>
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="F170" s="4" t="n">
-        <v>2.58</v>
+        <v>2.5838</v>
       </c>
       <c r="G170" s="4" t="n">
         <v>2.58</v>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>0.31</v>
+        <v>0.312</v>
       </c>
       <c r="G171" s="4" t="n">
         <v>0.31</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="F172" s="6" t="n">
-        <v>24.74</v>
+        <v>24.7403</v>
       </c>
       <c r="G172" s="6" t="n">
         <v>148.44</v>
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>2.58</v>
+        <v>2.5838</v>
       </c>
       <c r="G173" s="4" t="n">
         <v>2.58</v>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="F174" s="4" t="n">
-        <v>15.93</v>
+        <v>15.9348</v>
       </c>
       <c r="G174" s="4" t="n">
         <v>15.93</v>
@@ -7605,12 +7605,12 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-034.02 — Деталь 80×80×60,6</t>
+          <t xml:space="preserve">    PSH24-034.02 — Панель гнутая, s=3,6</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D175" s="4" t="n">
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>0.37</v>
+        <v>0.3745</v>
       </c>
       <c r="G175" s="4" t="n">
         <v>0.37</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -7646,12 +7646,12 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-034.03 — Деталь 126,5×80×80</t>
+          <t xml:space="preserve">    PSH24-034.03 — Панель гнутая, s=3,9</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D176" s="4" t="n">
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="F176" s="4" t="n">
-        <v>1.1</v>
+        <v>1.1016</v>
       </c>
       <c r="G176" s="4" t="n">
         <v>1.1</v>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -7687,12 +7687,12 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-034.04 — Деталь 223,4×80×80</t>
+          <t xml:space="preserve">    PSH24-034.04 — Панель гнутая, s=3,9</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D177" s="4" t="n">
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>2</v>
+        <v>1.9952</v>
       </c>
       <c r="G177" s="4" t="n">
         <v>2</v>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="F178" s="4" t="n">
-        <v>0.85</v>
+        <v>0.8524</v>
       </c>
       <c r="G178" s="4" t="n">
         <v>2.56</v>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>0.19</v>
+        <v>0.1931</v>
       </c>
       <c r="G179" s="4" t="n">
         <v>0.19</v>
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="F180" s="6" t="n">
-        <v>11.93</v>
+        <v>11.9254</v>
       </c>
       <c r="G180" s="6" t="n">
         <v>47.7</v>
@@ -7868,7 +7868,7 @@
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>2.58</v>
+        <v>2.5838</v>
       </c>
       <c r="G181" s="4" t="n">
         <v>2.58</v>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="F182" s="4" t="n">
-        <v>0.85</v>
+        <v>0.8524</v>
       </c>
       <c r="G182" s="4" t="n">
         <v>0.85</v>
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>6.12</v>
+        <v>6.1243</v>
       </c>
       <c r="G183" s="4" t="n">
         <v>6.12</v>
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="F184" s="4" t="n">
-        <v>2.36</v>
+        <v>2.3649</v>
       </c>
       <c r="G184" s="4" t="n">
         <v>2.36</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="F185" s="6" t="n">
-        <v>18.64</v>
+        <v>18.6384</v>
       </c>
       <c r="G185" s="6" t="n">
         <v>111.83</v>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="F186" s="4" t="n">
-        <v>14.58</v>
+        <v>14.5822</v>
       </c>
       <c r="G186" s="4" t="n">
         <v>14.58</v>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>2.58</v>
+        <v>2.5838</v>
       </c>
       <c r="G187" s="4" t="n">
         <v>2.58</v>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-036.03 — Стержень ⌀20, L=150</t>
+          <t xml:space="preserve">    PSH24-036.03 — Деталь 150×20×20</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D188" s="4" t="n">
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="F188" s="4" t="n">
-        <v>0.37</v>
+        <v>0.3681</v>
       </c>
       <c r="G188" s="4" t="n">
         <v>1.47</v>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>стержневая</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="F189" s="6" t="n">
-        <v>38.19</v>
+        <v>38.1877</v>
       </c>
       <c r="G189" s="6" t="n">
         <v>38.19</v>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="F190" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="G190" s="4" t="n">
         <v>0.21</v>
@@ -8261,12 +8261,12 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-041.01 — Труба ⌀480,9×1,3, L=1510</t>
+          <t xml:space="preserve">    PSH24-041.01 — Панель гнутая, s=2</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D191" s="4" t="n">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="F191" s="4" t="n">
-        <v>22.71</v>
+        <v>22.7103</v>
       </c>
       <c r="G191" s="4" t="n">
         <v>22.71</v>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="F192" s="4" t="n">
-        <v>2.75</v>
+        <v>2.7491</v>
       </c>
       <c r="G192" s="4" t="n">
         <v>5.5</v>
@@ -8343,12 +8343,12 @@
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-041.03 — Труба профильная 120×55×2,4, L=1510</t>
+          <t xml:space="preserve">    PSH24-041.03 — Деталь 1510×120×55</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D193" s="4" t="n">
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="F193" s="4" t="n">
-        <v>9.77</v>
+        <v>9.770099999999999</v>
       </c>
       <c r="G193" s="4" t="n">
         <v>9.77</v>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,7 @@
         </is>
       </c>
       <c r="F194" s="6" t="n">
-        <v>237.26</v>
+        <v>237.2586</v>
       </c>
       <c r="G194" s="6" t="n">
         <v>237.26</v>
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="F196" s="4" t="n">
-        <v>7.21</v>
+        <v>7.2109</v>
       </c>
       <c r="G196" s="4" t="n">
         <v>14.42</v>
@@ -8507,12 +8507,12 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-042.03 — Стержень ⌀95, L=2052</t>
+          <t xml:space="preserve">    PSH24-042.03 — Деталь 2052×95×95</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D197" s="4" t="n">
@@ -8524,7 +8524,7 @@
         </is>
       </c>
       <c r="F197" s="4" t="n">
-        <v>109.38</v>
+        <v>109.3768</v>
       </c>
       <c r="G197" s="4" t="n">
         <v>109.38</v>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>стержневая</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="F198" s="6" t="n">
-        <v>242.02</v>
+        <v>242.0198</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>242.02</v>
@@ -8606,7 +8606,7 @@
         </is>
       </c>
       <c r="F199" s="4" t="n">
-        <v>170.99</v>
+        <v>170.989</v>
       </c>
       <c r="G199" s="4" t="n">
         <v>170.99</v>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="F200" s="4" t="n">
-        <v>7.51</v>
+        <v>7.5142</v>
       </c>
       <c r="G200" s="4" t="n">
         <v>15.03</v>
@@ -8671,12 +8671,12 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-043.03 — Стержень ⌀75, L=1660</t>
+          <t xml:space="preserve">    PSH24-043.03 — Деталь 1660×75×75</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D201" s="4" t="n">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>56</v>
+        <v>56.0023</v>
       </c>
       <c r="G201" s="4" t="n">
         <v>56</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>стержневая</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="F202" s="6" t="n">
-        <v>17.54</v>
+        <v>17.5425</v>
       </c>
       <c r="G202" s="6" t="n">
         <v>35.09</v>
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>0.4</v>
+        <v>0.4048</v>
       </c>
       <c r="G203" s="4" t="n">
         <v>0.4</v>
@@ -8794,12 +8794,12 @@
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-044.01 — Профиль сплошной 100×20, L=326</t>
+          <t xml:space="preserve">    PSH24-044.01 — Деталь 326×100×20</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D204" s="4" t="n">
@@ -8811,7 +8811,7 @@
         </is>
       </c>
       <c r="F204" s="4" t="n">
-        <v>4.93</v>
+        <v>4.9288</v>
       </c>
       <c r="G204" s="4" t="n">
         <v>4.93</v>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -8835,12 +8835,12 @@
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-044.02 — Деталь 336×192×140</t>
+          <t xml:space="preserve">    PSH24-044.02 — Панель гнутая, s=2</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D205" s="4" t="n">
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="F205" s="4" t="n">
-        <v>1.26</v>
+        <v>1.2552</v>
       </c>
       <c r="G205" s="4" t="n">
         <v>1.26</v>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -8876,12 +8876,12 @@
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-044.03 — Деталь 340×192×140</t>
+          <t xml:space="preserve">    PSH24-044.03 — Панель гнутая, s=1,9</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D206" s="4" t="n">
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="F206" s="4" t="n">
-        <v>1.25</v>
+        <v>1.2517</v>
       </c>
       <c r="G206" s="4" t="n">
         <v>1.25</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="F207" s="4" t="n">
-        <v>5.24</v>
+        <v>5.2391</v>
       </c>
       <c r="G207" s="4" t="n">
         <v>5.24</v>
@@ -8975,7 +8975,7 @@
         </is>
       </c>
       <c r="F208" s="4" t="n">
-        <v>0.47</v>
+        <v>0.4678</v>
       </c>
       <c r="G208" s="4" t="n">
         <v>0.47</v>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-044.06 — Стержень ⌀36, L=500</t>
+          <t xml:space="preserve">    PSH24-044.06 — Деталь 500×36×36</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D209" s="4" t="n">
@@ -9016,7 +9016,7 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>4</v>
+        <v>3.9952</v>
       </c>
       <c r="G209" s="4" t="n">
         <v>4</v>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>стержневая</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="F210" s="6" t="n">
-        <v>298.88</v>
+        <v>298.8794</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>298.88</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>42.79</v>
+        <v>42.7917</v>
       </c>
       <c r="G211" s="4" t="n">
         <v>42.79</v>
@@ -9139,7 +9139,7 @@
         </is>
       </c>
       <c r="F212" s="6" t="n">
-        <v>38.41</v>
+        <v>38.4071</v>
       </c>
       <c r="G212" s="6" t="n">
         <v>38.41</v>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        PSH20-051.01 — Труба профильная 455×60×2,9, L=1550</t>
+          <t xml:space="preserve">        PSH20-051.01 — Деталь 1550×455×60</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D213" s="4" t="n">
@@ -9180,7 +9180,7 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>35.59</v>
+        <v>35.5893</v>
       </c>
       <c r="G213" s="4" t="n">
         <v>35.59</v>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        PSH20-051.02 — Профиль сплошной 54×5, L=445</t>
+          <t xml:space="preserve">        PSH20-051.02 — Полоса 54×5, L=445</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="D214" s="4" t="n">
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="F214" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9393</v>
       </c>
       <c r="G214" s="4" t="n">
         <v>2.82</v>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая</t>
         </is>
       </c>
     </row>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-050.01 — Деталь 1550×1027,1×95,1</t>
+          <t xml:space="preserve">    PSH24-050.01 — Панель гнутая, s=3</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D215" s="4" t="n">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>38.56</v>
+        <v>38.5575</v>
       </c>
       <c r="G215" s="4" t="n">
         <v>38.56</v>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="F216" s="4" t="n">
-        <v>16.25</v>
+        <v>16.2543</v>
       </c>
       <c r="G216" s="4" t="n">
         <v>32.51</v>
@@ -9327,12 +9327,12 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-050.05 — Труба профильная 80×60×3,8, L=1320</t>
+          <t xml:space="preserve">    PSH24-050.05 — Деталь 1320×80×60</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D217" s="4" t="n">
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="F217" s="4" t="n">
-        <v>10.41</v>
+        <v>10.4097</v>
       </c>
       <c r="G217" s="4" t="n">
         <v>10.41</v>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -9368,12 +9368,12 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-050.06 — Деталь 946×696×30</t>
+          <t xml:space="preserve">    PSH24-050.06 — Панель гнутая, s=3</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D218" s="4" t="n">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="F218" s="4" t="n">
-        <v>17.32</v>
+        <v>17.3234</v>
       </c>
       <c r="G218" s="4" t="n">
         <v>17.32</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-052.01 — Деталь 764×455×105</t>
+          <t xml:space="preserve">    PSH24-052.01 — Панель гнутая, s=5,9</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D219" s="4" t="n">
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="F219" s="4" t="n">
-        <v>25.4</v>
+        <v>25.3982</v>
       </c>
       <c r="G219" s="4" t="n">
         <v>25.4</v>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-052.01-01 — Деталь 764×455×105</t>
+          <t xml:space="preserve">    PSH24-052.01-01 — Панель гнутая, s=5,9</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D220" s="4" t="n">
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="F220" s="4" t="n">
-        <v>25.4</v>
+        <v>25.3982</v>
       </c>
       <c r="G220" s="4" t="n">
         <v>25.4</v>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="F221" s="6" t="n">
-        <v>33.25</v>
+        <v>33.2511</v>
       </c>
       <c r="G221" s="6" t="n">
         <v>33.25</v>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="F222" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="G222" s="4" t="n">
         <v>0.19</v>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="F223" s="4" t="n">
-        <v>33.06</v>
+        <v>33.0611</v>
       </c>
       <c r="G223" s="4" t="n">
         <v>33.06</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="F224" s="6" t="n">
-        <v>33.25</v>
+        <v>33.2511</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>33.25</v>
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="F225" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="G225" s="4" t="n">
         <v>0.19</v>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="F226" s="4" t="n">
-        <v>33.06</v>
+        <v>33.0611</v>
       </c>
       <c r="G226" s="4" t="n">
         <v>33.06</v>
@@ -9754,7 +9754,7 @@
         </is>
       </c>
       <c r="F227" s="6" t="n">
-        <v>0.79</v>
+        <v>0.7914</v>
       </c>
       <c r="G227" s="6" t="n">
         <v>0.79</v>
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="F228" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="G228" s="4" t="n">
         <v>0.02</v>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="F229" s="4" t="n">
-        <v>0.49</v>
+        <v>0.4886</v>
       </c>
       <c r="G229" s="4" t="n">
         <v>0.49</v>
@@ -9877,7 +9877,7 @@
         </is>
       </c>
       <c r="F230" s="4" t="n">
-        <v>0.22</v>
+        <v>0.2178</v>
       </c>
       <c r="G230" s="4" t="n">
         <v>0.22</v>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="F231" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="G231" s="4" t="n">
         <v>0.07000000000000001</v>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="F232" s="6" t="n">
-        <v>0.79</v>
+        <v>0.7914</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>0.79</v>
@@ -10000,7 +10000,7 @@
         </is>
       </c>
       <c r="F233" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="G233" s="4" t="n">
         <v>0.02</v>
@@ -10041,7 +10041,7 @@
         </is>
       </c>
       <c r="F234" s="4" t="n">
-        <v>0.49</v>
+        <v>0.4886</v>
       </c>
       <c r="G234" s="4" t="n">
         <v>0.49</v>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="F235" s="4" t="n">
-        <v>0.22</v>
+        <v>0.2178</v>
       </c>
       <c r="G235" s="4" t="n">
         <v>0.22</v>
@@ -10123,7 +10123,7 @@
         </is>
       </c>
       <c r="F236" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="G236" s="4" t="n">
         <v>0.07000000000000001</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="F237" s="6" t="n">
-        <v>7.29</v>
+        <v>7.2873</v>
       </c>
       <c r="G237" s="6" t="n">
         <v>7.29</v>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="F238" s="4" t="n">
-        <v>0.06</v>
+        <v>0.0582</v>
       </c>
       <c r="G238" s="4" t="n">
         <v>0.12</v>
@@ -10229,12 +10229,12 @@
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-060.01 — Труба ⌀40×2,4, L=850</t>
+          <t xml:space="preserve">    PSH24-060.01 — Деталь 850×40×40</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D239" s="4" t="n">
@@ -10246,7 +10246,7 @@
         </is>
       </c>
       <c r="F239" s="4" t="n">
-        <v>1.92</v>
+        <v>1.918</v>
       </c>
       <c r="G239" s="4" t="n">
         <v>1.92</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-060.01-01 — Труба ⌀40×2,4, L=850</t>
+          <t xml:space="preserve">    PSH24-060.01-01 — Деталь 850×40×40</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D240" s="4" t="n">
@@ -10287,7 +10287,7 @@
         </is>
       </c>
       <c r="F240" s="4" t="n">
-        <v>1.92</v>
+        <v>1.918</v>
       </c>
       <c r="G240" s="4" t="n">
         <v>1.92</v>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -10311,12 +10311,12 @@
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-060.02 — Труба ⌀36×2,4, L=1050</t>
+          <t xml:space="preserve">    PSH24-060.02 — Деталь 1050×36×36</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D241" s="4" t="n">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="F241" s="4" t="n">
-        <v>2.05</v>
+        <v>2.0537</v>
       </c>
       <c r="G241" s="4" t="n">
         <v>2.05</v>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -10352,12 +10352,12 @@
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-060.03 — Труба ⌀36×2,1, L=350</t>
+          <t xml:space="preserve">    PSH24-060.03 — Деталь 350×36×36</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D242" s="4" t="n">
@@ -10369,7 +10369,7 @@
         </is>
       </c>
       <c r="F242" s="4" t="n">
-        <v>0.62</v>
+        <v>0.6157</v>
       </c>
       <c r="G242" s="4" t="n">
         <v>0.62</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="I242" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="F243" s="6" t="n">
-        <v>0.67</v>
+        <v>0.6656</v>
       </c>
       <c r="G243" s="6" t="n">
         <v>0.67</v>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        PSH24-061.01 — Труба профильная 60×41,4×1,2, L=248,4</t>
+          <t xml:space="preserve">        PSH24-061.01 — Панель гнутая, s=3,7</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D244" s="4" t="n">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="F244" s="4" t="n">
-        <v>0.48</v>
+        <v>0.4791</v>
       </c>
       <c r="G244" s="4" t="n">
         <v>0.48</v>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="I244" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="F245" s="4" t="n">
-        <v>0.09</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G245" s="4" t="n">
         <v>0.19</v>
@@ -10533,7 +10533,7 @@
         </is>
       </c>
       <c r="F246" s="6" t="n">
-        <v>30.16</v>
+        <v>30.1648</v>
       </c>
       <c r="G246" s="6" t="n">
         <v>30.16</v>
@@ -10574,7 +10574,7 @@
         </is>
       </c>
       <c r="F247" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0113</v>
       </c>
       <c r="G247" s="4" t="n">
         <v>0.01</v>
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="F248" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0113</v>
       </c>
       <c r="G248" s="4" t="n">
         <v>0.05</v>
@@ -10656,7 +10656,7 @@
         </is>
       </c>
       <c r="F249" s="4" t="n">
-        <v>0.03</v>
+        <v>0.0344</v>
       </c>
       <c r="G249" s="4" t="n">
         <v>0.14</v>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="F250" s="4" t="n">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="G250" s="4" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="F251" s="6" t="n">
-        <v>0.01</v>
+        <v>0.0124</v>
       </c>
       <c r="G251" s="6" t="n">
         <v>0.05</v>
@@ -10779,7 +10779,7 @@
         </is>
       </c>
       <c r="F252" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0069</v>
       </c>
       <c r="G252" s="4" t="n">
         <v>0.01</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="F253" s="4" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G253" s="4" t="n">
         <v>0</v>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="F254" s="4" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="G254" s="4" t="n">
         <v>0</v>
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="F255" s="4" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="G255" s="4" t="n">
         <v>0</v>
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="F256" s="4" t="n">
-        <v>0.13</v>
+        <v>0.1265</v>
       </c>
       <c r="G256" s="4" t="n">
         <v>0.13</v>
@@ -10984,7 +10984,7 @@
         </is>
       </c>
       <c r="F257" s="4" t="n">
-        <v>0.17</v>
+        <v>0.1719</v>
       </c>
       <c r="G257" s="4" t="n">
         <v>0.17</v>
@@ -11008,12 +11008,12 @@
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-070.01 — Деталь 1184×500×50</t>
+          <t xml:space="preserve">    PSH24-070.01 — Панель гнутая, s=4,9</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D258" s="4" t="n">
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="F258" s="4" t="n">
-        <v>25.93</v>
+        <v>25.9258</v>
       </c>
       <c r="G258" s="4" t="n">
         <v>25.93</v>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -11049,12 +11049,12 @@
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-070.02 — Труба профильная 35,4×19×1,4, L=1174</t>
+          <t xml:space="preserve">    PSH24-070.02 — Деталь 1174×35,4×19</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D259" s="4" t="n">
@@ -11066,7 +11066,7 @@
         </is>
       </c>
       <c r="F259" s="4" t="n">
-        <v>1.32</v>
+        <v>1.3153</v>
       </c>
       <c r="G259" s="4" t="n">
         <v>1.32</v>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>профильная</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -11090,12 +11090,12 @@
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-070.03 — Стержень ⌀16, L=500</t>
+          <t xml:space="preserve">    PSH24-070.03 — Деталь 500×16×16</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D260" s="4" t="n">
@@ -11107,7 +11107,7 @@
         </is>
       </c>
       <c r="F260" s="4" t="n">
-        <v>0.79</v>
+        <v>0.7892</v>
       </c>
       <c r="G260" s="4" t="n">
         <v>1.58</v>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>стержневая</t>
+          <t>механическая</t>
         </is>
       </c>
     </row>
@@ -11131,12 +11131,12 @@
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    PSH24-070.04 — Деталь 86×80×60</t>
+          <t xml:space="preserve">    PSH24-070.04 — Панель гнутая, s=2,7</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="D261" s="4" t="n">
@@ -11148,7 +11148,7 @@
         </is>
       </c>
       <c r="F261" s="4" t="n">
-        <v>0.27</v>
+        <v>0.2749</v>
       </c>
       <c r="G261" s="4" t="n">
         <v>0.27</v>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>механическая</t>
+          <t>листовая гнутая</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="F262" s="6" t="n">
-        <v>0.52</v>
+        <v>0.5245</v>
       </c>
       <c r="G262" s="6" t="n">
         <v>0.52</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="F263" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0743</v>
       </c>
       <c r="G263" s="4" t="n">
         <v>0.07000000000000001</v>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F264" s="4" t="n">
-        <v>0.43</v>
+        <v>0.4307</v>
       </c>
       <c r="G264" s="4" t="n">
         <v>0.43</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="F265" s="4" t="n">
-        <v>0.02</v>
+        <v>0.0195</v>
       </c>
       <c r="G265" s="4" t="n">
         <v>0.02</v>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="F266" s="6" t="n">
-        <v>6.86</v>
+        <v>6.8618</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>13.72</v>
@@ -11394,7 +11394,7 @@
         </is>
       </c>
       <c r="F267" s="4" t="n">
-        <v>0</v>
+        <v>0.0028</v>
       </c>
       <c r="G267" s="4" t="n">
         <v>0</v>
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="F268" s="4" t="n">
-        <v>0.02</v>
+        <v>0.0219</v>
       </c>
       <c r="G268" s="4" t="n">
         <v>0.22</v>
@@ -11476,7 +11476,7 @@
         </is>
       </c>
       <c r="F269" s="4" t="n">
-        <v>1.73</v>
+        <v>1.7257</v>
       </c>
       <c r="G269" s="4" t="n">
         <v>1.73</v>
@@ -11517,7 +11517,7 @@
         </is>
       </c>
       <c r="F270" s="4" t="n">
-        <v>4.91</v>
+        <v>4.9144</v>
       </c>
       <c r="G270" s="4" t="n">
         <v>4.91</v>
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="F271" s="6" t="n">
-        <v>13.71</v>
+        <v>13.7143</v>
       </c>
       <c r="G271" s="6" t="n">
         <v>27.43</v>
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="F272" s="4" t="n">
-        <v>0</v>
+        <v>0.0028</v>
       </c>
       <c r="G272" s="4" t="n">
         <v>0</v>
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="F273" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0451</v>
       </c>
       <c r="G273" s="4" t="n">
         <v>0.45</v>
@@ -11681,7 +11681,7 @@
         </is>
       </c>
       <c r="F274" s="4" t="n">
-        <v>3.65</v>
+        <v>3.6503</v>
       </c>
       <c r="G274" s="4" t="n">
         <v>3.65</v>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="F276" s="4" t="n">
-        <v>7.53</v>
+        <v>7.5261</v>
       </c>
       <c r="G276" s="4" t="n">
         <v>7.53</v>
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="F277" s="4" t="n">
-        <v>14.33</v>
+        <v>14.3291</v>
       </c>
       <c r="G277" s="4" t="n">
         <v>14.33</v>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="F278" s="4" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="G278" s="4" t="n">
         <v>0</v>
@@ -11886,7 +11886,7 @@
         </is>
       </c>
       <c r="F279" s="4" t="n">
-        <v>0.04</v>
+        <v>0.043</v>
       </c>
       <c r="G279" s="4" t="n">
         <v>0.09</v>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 455×60×2,9, L=1550</t>
+          <t>Деталь 1550×455×60</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 54×5, L=445</t>
+          <t>Полоса 54×5, L=445</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Профиль резиновый 1200×346,4, L=6276,8</t>
+          <t>Полотно гибкое (резина), s=5</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Деталь 250,5×244×130,5</t>
+          <t>Панель гнутая, s=4,7</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Деталь 250,5×230,2×139</t>
+          <t>Панель гнутая, s=4,7</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 40×3, L=5600</t>
+          <t>Полоса 40×3, L=5600</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Профиль резиновый 171×32,8, L=5700</t>
+          <t>Полотно гибкое (резина), s=4,9</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Стержень ⌀63, L=1026</t>
+          <t>Деталь 1026×63×63</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Комплектующее покупное (см. спецификацию)</t>
+          <t>Ст3сп5, ГОСТ 380-2005 (принято по умолчанию)</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Труба ⌀108×13,1, L=1338</t>
+          <t>Деталь 1338×108×108</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Комплектующее покупное (см. спецификацию)</t>
+          <t>Ст3сп5, ГОСТ 380-2005 (принято по умолчанию)</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 105×15, L=1260</t>
+          <t>Деталь 1260×105×15</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 40×3, L=1260</t>
+          <t>Полоса 40×3, L=1260</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 60×8, L=850</t>
+          <t>Полоса 60×8, L=850</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 40×3, L=850</t>
+          <t>Полоса 40×3, L=850</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 105×8, L=1330</t>
+          <t>Полоса резиновая 105×8, L=1330</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 168,7×62×2, L=5720</t>
+          <t>Панель гнутая, s=4,8</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 168,7×62×2, L=5720</t>
+          <t>Панель гнутая, s=4,8</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 175×3, L=750</t>
+          <t>Полоса 175×3, L=750</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,3, L=3500</t>
+          <t>Деталь 3500×451×105</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,3, L=3500</t>
+          <t>Деталь 3500×451×105</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 79×6, L=437</t>
+          <t>Полоса 79×6, L=437</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,5, L=2105</t>
+          <t>Деталь 2105×451×105</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,5, L=2105</t>
+          <t>Деталь 2105×451×105</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Деталь 1561,4×1250×138,1</t>
+          <t>Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 112,9×5×1,5, L=1546,5</t>
+          <t>Полоса 112,9×5, L=1546,5</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 112,9×5×1,4, L=1548</t>
+          <t>Полоса 112,9×5, L=1548</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 250×138,1×1,8, L=1561,4</t>
+          <t>Панель гнутая, s=4,9</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×6, L=1506</t>
+          <t>Полоса 80×6, L=1506</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×5, L=3004</t>
+          <t>Полоса 80×5, L=3004</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×6, L=1323</t>
+          <t>Полоса 80×6, L=1323</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×6, L=800</t>
+          <t>Полоса 80×6, L=800</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×6, L=743</t>
+          <t>Полоса 80×6, L=743</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×6, L=410</t>
+          <t>Полоса 80×6, L=410</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×6, L=1423</t>
+          <t>Полоса 80×6, L=1423</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×6, L=568</t>
+          <t>Полоса 80×6, L=568</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×6, L=1305</t>
+          <t>Полоса 80×6, L=1305</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×6, L=1210</t>
+          <t>Полоса 80×6, L=1210</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Труба ⌀30×2, L=894</t>
+          <t>Деталь 894×30×30</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 600×85×2,8, L=3004</t>
+          <t>Деталь 3004×600×85</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 600×85×2,8, L=3004</t>
+          <t>Деталь 3004×600×85</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 80×5, L=590</t>
+          <t>Полоса 80×5, L=590</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>plate</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -15084,7 +15084,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 600×85×2,9, L=2500</t>
+          <t>Деталь 2500×600×85</t>
         </is>
       </c>
       <c r="D65" s="4" t="n">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Деталь 1561,4×1000×138,1</t>
+          <t>Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Деталь 1561,4×1000×138,1</t>
+          <t>Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 80×45×4,9, L=2128</t>
+          <t>Деталь 2128×80×45</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Труба ⌀50×3,3, L=1410</t>
+          <t>Деталь 1410×50×50</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Труба ⌀50×3,3, L=1207</t>
+          <t>Деталь 1207×50×50</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Деталь 80×80×60,6</t>
+          <t>Панель гнутая, s=3,6</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Деталь 126,5×80×80</t>
+          <t>Панель гнутая, s=3,9</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
@@ -15946,7 +15946,7 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Деталь 223,4×80×80</t>
+          <t>Панель гнутая, s=3,9</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -16309,7 +16309,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Стержень ⌀20, L=150</t>
+          <t>Деталь 150×20×20</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Труба ⌀480,9×1,3, L=1510</t>
+          <t>Панель гнутая, s=2</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -16456,7 +16456,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 120×55×2,4, L=1510</t>
+          <t>Деталь 1510×120×55</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
@@ -16485,7 +16485,7 @@
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
@@ -16603,7 +16603,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Стержень ⌀95, L=2052</t>
+          <t>Деталь 2052×95×95</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Стержень ⌀75, L=1660</t>
+          <t>Деталь 1660×75×75</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 100×20, L=326</t>
+          <t>Деталь 326×100×20</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Деталь 336×192×140</t>
+          <t>Панель гнутая, s=2</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Деталь 340×192×140</t>
+          <t>Панель гнутая, s=1,9</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
@@ -17044,7 +17044,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Стержень ⌀36, L=500</t>
+          <t>Деталь 500×36×36</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
@@ -17073,7 +17073,7 @@
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
@@ -17093,7 +17093,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Деталь 1550×1027,1×95,1</t>
+          <t>Панель гнутая, s=3</t>
         </is>
       </c>
       <c r="D106" s="4" t="n">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 80×60×3,8, L=1320</t>
+          <t>Деталь 1320×80×60</t>
         </is>
       </c>
       <c r="D108" s="4" t="n">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Деталь 946×696×30</t>
+          <t>Панель гнутая, s=3</t>
         </is>
       </c>
       <c r="D109" s="4" t="n">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Деталь 764×455×105</t>
+          <t>Панель гнутая, s=5,9</t>
         </is>
       </c>
       <c r="D110" s="4" t="n">
@@ -17318,7 +17318,7 @@
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Деталь 764×455×105</t>
+          <t>Панель гнутая, s=5,9</t>
         </is>
       </c>
       <c r="D111" s="4" t="n">
@@ -17367,7 +17367,7 @@
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Труба ⌀40×2,4, L=850</t>
+          <t>Деталь 850×40×40</t>
         </is>
       </c>
       <c r="D117" s="4" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Труба ⌀40×2,4, L=850</t>
+          <t>Деталь 850×40×40</t>
         </is>
       </c>
       <c r="D118" s="4" t="n">
@@ -17710,7 +17710,7 @@
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
@@ -17730,7 +17730,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Труба ⌀36×2,4, L=1050</t>
+          <t>Деталь 1050×36×36</t>
         </is>
       </c>
       <c r="D119" s="4" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Труба ⌀36×2,1, L=350</t>
+          <t>Деталь 350×36×36</t>
         </is>
       </c>
       <c r="D120" s="4" t="n">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr">
@@ -17828,7 +17828,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 60×41,4×1,2, L=248,4</t>
+          <t>Панель гнутая, s=3,7</t>
         </is>
       </c>
       <c r="D121" s="4" t="n">
@@ -17857,7 +17857,7 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Деталь 1184×500×50</t>
+          <t>Панель гнутая, s=4,9</t>
         </is>
       </c>
       <c r="D123" s="4" t="n">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Труба профильная 35,4×19×1,4, L=1174</t>
+          <t>Деталь 1174×35,4×19</t>
         </is>
       </c>
       <c r="D124" s="4" t="n">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>tube</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Стержень ⌀16, L=500</t>
+          <t>Деталь 500×16×16</t>
         </is>
       </c>
       <c r="D125" s="4" t="n">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>shaft</t>
+          <t>other</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Деталь 86×80×60</t>
+          <t>Панель гнутая, s=2,7</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bent</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr">
